--- a/docs/Logic Requirements/Ageipelago Montezuma.xlsx
+++ b/docs/Logic Requirements/Ageipelago Montezuma.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A599EB4-0E69-49C9-9AFB-167A96F4B5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9830BC-02A3-497A-8CF3-7EABA2870B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{17AA2DA1-B674-46E5-8909-131BC3A5F213}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="192">
   <si>
     <t>Scenario</t>
   </si>
@@ -3181,12 +3181,50 @@
   <si>
     <t>Requires Transport Ship</t>
   </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Feudal - Castle Age</t>
+  </si>
+  <si>
+    <t>No Monastery</t>
+  </si>
+  <si>
+    <t>Caravel</t>
+  </si>
+  <si>
+    <t>Requires Transport Ship
+Only Hard Logic</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>No Catapult Galleon
+No Xolotl Warrior</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3317,6 +3355,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3326,7 +3371,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -3462,11 +3507,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3565,6 +3634,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4182,15 +4275,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3AB02A6-6705-462C-AFB4-F8F81317FF41}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -4204,7 +4303,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="13" t="s">
         <v>76</v>
       </c>
@@ -4218,7 +4322,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>109</v>
       </c>
@@ -4232,7 +4345,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>185</v>
+      </c>
       <c r="G5" s="10" t="s">
         <v>110</v>
       </c>
@@ -4246,7 +4368,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="10" t="s">
         <v>111</v>
       </c>
@@ -4260,7 +4385,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>82</v>
       </c>
@@ -4274,7 +4402,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>113</v>
       </c>
@@ -4288,7 +4419,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>114</v>
       </c>
@@ -4302,7 +4436,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>91</v>
       </c>
@@ -4316,7 +4453,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="19" t="s">
         <v>115</v>
       </c>
@@ -4330,7 +4470,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="19" t="s">
         <v>116</v>
       </c>
@@ -4344,7 +4487,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="19" t="s">
         <v>85</v>
       </c>
@@ -4358,7 +4504,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="19" t="s">
         <v>98</v>
       </c>
@@ -4372,7 +4521,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="19" t="s">
         <v>106</v>
       </c>
@@ -4386,7 +4538,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="20" t="s">
         <v>117</v>
       </c>
@@ -4569,6 +4724,10 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -4576,15 +4735,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D318CCD2-3435-443A-AA52-8195CCD9461A}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -4598,7 +4763,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="13" t="s">
         <v>110</v>
       </c>
@@ -4612,7 +4782,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>111</v>
       </c>
@@ -4626,7 +4805,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>185</v>
+      </c>
       <c r="G5" s="10" t="s">
         <v>122</v>
       </c>
@@ -4640,7 +4828,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="15" t="s">
         <v>82</v>
       </c>
@@ -4654,7 +4845,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>123</v>
       </c>
@@ -4668,7 +4862,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>115</v>
       </c>
@@ -4682,7 +4879,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>124</v>
       </c>
@@ -4696,7 +4896,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>85</v>
       </c>
@@ -4710,7 +4913,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="15" t="s">
         <v>89</v>
       </c>
@@ -4724,7 +4930,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>104</v>
       </c>
@@ -4738,7 +4947,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="15" t="s">
         <v>105</v>
       </c>
@@ -4752,7 +4964,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="24" t="s">
         <v>84</v>
       </c>
@@ -4766,7 +4981,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="24" t="s">
         <v>113</v>
       </c>
@@ -4780,7 +4998,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="24" t="s">
         <v>106</v>
       </c>
@@ -4850,37 +5071,53 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G21" s="19" t="s">
         <v>118</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-    </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="K21" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G22" s="25" t="s">
         <v>126</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K22" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K23" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="K24" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="22"/>
@@ -4987,21 +5224,31 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484DAF4A-DAC4-4168-AC16-D57BBA4F7C96}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5015,7 +5262,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="13" t="s">
         <v>128</v>
       </c>
@@ -5029,7 +5281,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>111</v>
       </c>
@@ -5043,7 +5304,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>185</v>
+      </c>
       <c r="G5" s="15" t="s">
         <v>82</v>
       </c>
@@ -5057,7 +5327,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="15" t="s">
         <v>130</v>
       </c>
@@ -5071,7 +5344,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>131</v>
       </c>
@@ -5085,7 +5361,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>132</v>
       </c>
@@ -5099,7 +5378,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>133</v>
       </c>
@@ -5113,7 +5395,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>134</v>
       </c>
@@ -5127,7 +5412,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="15" t="s">
         <v>135</v>
       </c>
@@ -5141,7 +5429,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>136</v>
       </c>
@@ -5155,7 +5446,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="15" t="s">
         <v>137</v>
       </c>
@@ -5169,7 +5463,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="15" t="s">
         <v>100</v>
       </c>
@@ -5183,7 +5480,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="15" t="s">
         <v>129</v>
       </c>
@@ -5197,7 +5497,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="14" t="s">
         <v>138</v>
       </c>
@@ -5428,21 +5731,31 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE449FBF-0F17-4D22-AA89-F09A1B96E52D}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5456,7 +5769,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="13" t="s">
         <v>110</v>
       </c>
@@ -5470,7 +5788,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>111</v>
       </c>
@@ -5484,7 +5811,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>185</v>
+      </c>
       <c r="G5" s="10" t="s">
         <v>128</v>
       </c>
@@ -5498,7 +5834,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="10" t="s">
         <v>146</v>
       </c>
@@ -5512,7 +5851,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="10" t="s">
         <v>147</v>
       </c>
@@ -5526,7 +5868,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>115</v>
       </c>
@@ -5540,7 +5885,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>125</v>
       </c>
@@ -5554,7 +5902,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>148</v>
       </c>
@@ -5568,7 +5919,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="15" t="s">
         <v>98</v>
       </c>
@@ -5582,7 +5936,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>89</v>
       </c>
@@ -5596,7 +5953,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="15" t="s">
         <v>82</v>
       </c>
@@ -5610,7 +5970,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="15" t="s">
         <v>124</v>
       </c>
@@ -5624,7 +5987,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>140</v>
       </c>
@@ -5638,7 +6004,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="14" t="s">
         <v>149</v>
       </c>
@@ -5865,6 +6234,10 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -5872,15 +6245,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD5D7B81-02BA-4052-9F47-725EAD681E49}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5894,7 +6273,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="13" t="s">
         <v>110</v>
       </c>
@@ -5908,7 +6292,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="G4" s="30" t="s">
         <v>111</v>
       </c>
@@ -5922,7 +6315,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>185</v>
+      </c>
       <c r="G5" s="29" t="s">
         <v>124</v>
       </c>
@@ -5936,7 +6338,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="15" t="s">
         <v>159</v>
       </c>
@@ -5950,7 +6355,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>160</v>
       </c>
@@ -5964,7 +6372,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>82</v>
       </c>
@@ -5978,7 +6389,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>161</v>
       </c>
@@ -5992,7 +6406,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>85</v>
       </c>
@@ -6006,7 +6423,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="15" t="s">
         <v>129</v>
       </c>
@@ -6020,7 +6440,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>91</v>
       </c>
@@ -6034,7 +6457,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="10" t="s">
         <v>162</v>
       </c>
@@ -6048,7 +6474,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="15" t="s">
         <v>155</v>
       </c>
@@ -6062,7 +6491,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>151</v>
       </c>
@@ -6076,7 +6508,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="14" t="s">
         <v>139</v>
       </c>
@@ -6307,21 +6742,31 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5207D59-AEA2-42AF-9AD1-593F3FB5CDAE}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -6335,7 +6780,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="31" t="s">
         <v>82</v>
       </c>
@@ -6349,7 +6799,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="G4" s="19" t="s">
         <v>123</v>
       </c>
@@ -6363,7 +6822,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>185</v>
+      </c>
       <c r="G5" s="19" t="s">
         <v>168</v>
       </c>
@@ -6377,7 +6845,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="19" t="s">
         <v>138</v>
       </c>
@@ -6391,7 +6862,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="19" t="s">
         <v>153</v>
       </c>
@@ -6405,7 +6879,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="19" t="s">
         <v>169</v>
       </c>
@@ -6419,7 +6896,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="19" t="s">
         <v>100</v>
       </c>
@@ -6433,7 +6913,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="19" t="s">
         <v>142</v>
       </c>
@@ -6447,7 +6930,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="19" t="s">
         <v>172</v>
       </c>
@@ -6461,7 +6947,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="14" t="s">
         <v>163</v>
       </c>
@@ -6475,7 +6964,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="14" t="s">
         <v>173</v>
       </c>
@@ -6489,7 +6981,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="14" t="s">
         <v>174</v>
       </c>
@@ -6503,7 +6998,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>175</v>
       </c>
@@ -6517,7 +7015,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="15" t="s">
         <v>115</v>
       </c>
@@ -6724,6 +7225,10 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Montezuma.xlsx
+++ b/docs/Logic Requirements/Ageipelago Montezuma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9830BC-02A3-497A-8CF3-7EABA2870B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD014651-35B4-4F60-A023-513EC1D2F628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{17AA2DA1-B674-46E5-8909-131BC3A5F213}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{17AA2DA1-B674-46E5-8909-131BC3A5F213}"/>
   </bookViews>
   <sheets>
     <sheet name="Montezuma" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="194">
   <si>
     <t>Scenario</t>
   </si>
@@ -3219,12 +3219,58 @@
     <t>No Catapult Galleon
 No Xolotl Warrior</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+Murder Holes are researched automatically</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+Imperial Age is researched automatically</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3361,6 +3407,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3636,6 +3688,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3652,12 +3710,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4285,11 +4337,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -4304,11 +4356,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="41"/>
       <c r="G3" s="13" t="s">
         <v>76</v>
       </c>
@@ -4345,7 +4397,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
       <c r="B5" s="30" t="s">
         <v>187</v>
       </c>
@@ -4353,7 +4405,7 @@
         <v>185</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>110</v>
@@ -4369,8 +4421,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="18"/>
       <c r="G6" s="10" t="s">
         <v>111</v>
@@ -4386,8 +4438,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>82</v>
@@ -4403,8 +4455,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>113</v>
@@ -4420,8 +4472,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>114</v>
@@ -4437,8 +4489,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>91</v>
@@ -4454,8 +4506,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="18"/>
       <c r="G11" s="19" t="s">
         <v>115</v>
@@ -4471,8 +4523,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="18"/>
       <c r="G12" s="19" t="s">
         <v>116</v>
@@ -4488,8 +4540,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="18"/>
       <c r="G13" s="19" t="s">
         <v>85</v>
@@ -4505,8 +4557,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="18"/>
       <c r="G14" s="19" t="s">
         <v>98</v>
@@ -4522,8 +4574,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="18"/>
       <c r="G15" s="19" t="s">
         <v>106</v>
@@ -4539,8 +4591,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="18"/>
       <c r="G16" s="20" t="s">
         <v>117</v>
@@ -4745,11 +4797,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -4764,11 +4816,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="41"/>
       <c r="G3" s="13" t="s">
         <v>110</v>
       </c>
@@ -4805,7 +4857,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
       <c r="B5" s="30" t="s">
         <v>185</v>
       </c>
@@ -4813,7 +4865,7 @@
         <v>185</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>122</v>
@@ -4829,8 +4881,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="18"/>
       <c r="G6" s="15" t="s">
         <v>82</v>
@@ -4846,8 +4898,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>123</v>
@@ -4863,8 +4915,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>115</v>
@@ -4880,8 +4932,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>124</v>
@@ -4897,8 +4949,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>85</v>
@@ -4914,8 +4966,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="18"/>
       <c r="G11" s="15" t="s">
         <v>89</v>
@@ -4931,8 +4983,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>104</v>
@@ -4948,8 +5000,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="18"/>
       <c r="G13" s="15" t="s">
         <v>105</v>
@@ -4965,8 +5017,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="18"/>
       <c r="G14" s="24" t="s">
         <v>84</v>
@@ -4982,8 +5034,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="18"/>
       <c r="G15" s="24" t="s">
         <v>113</v>
@@ -4999,8 +5051,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="18"/>
       <c r="G16" s="24" t="s">
         <v>106</v>
@@ -5244,11 +5296,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5263,11 +5315,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="41"/>
       <c r="G3" s="13" t="s">
         <v>128</v>
       </c>
@@ -5304,7 +5356,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
       <c r="B5" s="30" t="s">
         <v>185</v>
       </c>
@@ -5312,7 +5364,7 @@
         <v>191</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>82</v>
@@ -5328,8 +5380,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="18"/>
       <c r="G6" s="15" t="s">
         <v>130</v>
@@ -5345,8 +5397,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>131</v>
@@ -5362,8 +5414,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>132</v>
@@ -5379,8 +5431,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>133</v>
@@ -5396,8 +5448,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>134</v>
@@ -5413,8 +5465,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="18"/>
       <c r="G11" s="15" t="s">
         <v>135</v>
@@ -5430,8 +5482,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>136</v>
@@ -5447,8 +5499,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="18"/>
       <c r="G13" s="15" t="s">
         <v>137</v>
@@ -5464,8 +5516,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="18"/>
       <c r="G14" s="15" t="s">
         <v>100</v>
@@ -5481,8 +5533,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="18"/>
       <c r="G15" s="15" t="s">
         <v>129</v>
@@ -5498,8 +5550,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="18"/>
       <c r="G16" s="14" t="s">
         <v>138</v>
@@ -5751,11 +5803,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5770,11 +5822,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="41"/>
       <c r="G3" s="13" t="s">
         <v>110</v>
       </c>
@@ -5835,8 +5887,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="18"/>
       <c r="G6" s="10" t="s">
         <v>146</v>
@@ -5852,8 +5904,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="18"/>
       <c r="G7" s="10" t="s">
         <v>147</v>
@@ -5869,8 +5921,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>115</v>
@@ -5886,8 +5938,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>125</v>
@@ -5903,8 +5955,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>148</v>
@@ -5920,8 +5972,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="18"/>
       <c r="G11" s="15" t="s">
         <v>98</v>
@@ -5937,8 +5989,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>89</v>
@@ -5954,8 +6006,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="18"/>
       <c r="G13" s="15" t="s">
         <v>82</v>
@@ -5971,8 +6023,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="18"/>
       <c r="G14" s="15" t="s">
         <v>124</v>
@@ -5988,8 +6040,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>140</v>
@@ -6005,8 +6057,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="18"/>
       <c r="G16" s="14" t="s">
         <v>149</v>
@@ -6255,11 +6307,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -6274,11 +6326,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="41"/>
       <c r="G3" s="13" t="s">
         <v>110</v>
       </c>
@@ -6339,8 +6391,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="18"/>
       <c r="G6" s="15" t="s">
         <v>159</v>
@@ -6356,8 +6408,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>160</v>
@@ -6373,8 +6425,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>82</v>
@@ -6390,8 +6442,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>161</v>
@@ -6407,8 +6459,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="18"/>
       <c r="G10" s="15" t="s">
         <v>85</v>
@@ -6424,8 +6476,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="18"/>
       <c r="G11" s="15" t="s">
         <v>129</v>
@@ -6441,8 +6493,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>91</v>
@@ -6458,8 +6510,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="18"/>
       <c r="G13" s="10" t="s">
         <v>162</v>
@@ -6475,8 +6527,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="18"/>
       <c r="G14" s="15" t="s">
         <v>155</v>
@@ -6492,8 +6544,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>151</v>
@@ -6509,8 +6561,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="18"/>
       <c r="G16" s="14" t="s">
         <v>139</v>
@@ -6762,11 +6814,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -6781,11 +6833,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="41"/>
       <c r="G3" s="31" t="s">
         <v>82</v>
       </c>
@@ -6846,8 +6898,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="18"/>
       <c r="G6" s="19" t="s">
         <v>138</v>
@@ -6863,8 +6915,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="18"/>
       <c r="G7" s="19" t="s">
         <v>153</v>
@@ -6880,8 +6932,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="18"/>
       <c r="G8" s="19" t="s">
         <v>169</v>
@@ -6897,8 +6949,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="18"/>
       <c r="G9" s="19" t="s">
         <v>100</v>
@@ -6914,8 +6966,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="18"/>
       <c r="G10" s="19" t="s">
         <v>142</v>
@@ -6931,8 +6983,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="18"/>
       <c r="G11" s="19" t="s">
         <v>172</v>
@@ -6948,8 +7000,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="18"/>
       <c r="G12" s="14" t="s">
         <v>163</v>
@@ -6965,8 +7017,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="18"/>
       <c r="G13" s="14" t="s">
         <v>173</v>
@@ -6982,8 +7034,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="18"/>
       <c r="G14" s="14" t="s">
         <v>174</v>
@@ -6999,8 +7051,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>175</v>
@@ -7016,8 +7068,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="18"/>
       <c r="G16" s="15" t="s">
         <v>115</v>

--- a/docs/Logic Requirements/Ageipelago Montezuma.xlsx
+++ b/docs/Logic Requirements/Ageipelago Montezuma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD014651-35B4-4F60-A023-513EC1D2F628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547568EE-AC41-45E3-9EDB-E13935AC01E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{17AA2DA1-B674-46E5-8909-131BC3A5F213}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{17AA2DA1-B674-46E5-8909-131BC3A5F213}"/>
   </bookViews>
   <sheets>
     <sheet name="Montezuma" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="203">
   <si>
     <t>Scenario</t>
   </si>
@@ -3264,6 +3264,33 @@
       <t>:
 Imperial Age is researched automatically</t>
     </r>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Elite Skirmisher</t>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>Baracks</t>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <t>Xolotl Warrior</t>
   </si>
 </sst>
 </file>
@@ -3423,7 +3450,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -3583,11 +3610,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3691,9 +3729,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3712,6 +3747,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -4331,17 +4379,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -4356,11 +4405,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="13" t="s">
         <v>76</v>
       </c>
@@ -4437,7 +4486,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
       <c r="D7" s="18"/>
@@ -4454,10 +4503,19 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>113</v>
       </c>
@@ -4472,9 +4530,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="42"/>
+      <c r="E9" s="30" t="s">
+        <v>46</v>
+      </c>
       <c r="G9" s="15" t="s">
         <v>114</v>
       </c>
@@ -4489,9 +4554,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
       <c r="G10" s="15" t="s">
         <v>91</v>
       </c>
@@ -4506,9 +4576,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
       <c r="G11" s="19" t="s">
         <v>115</v>
       </c>
@@ -4523,9 +4594,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
       <c r="G12" s="19" t="s">
         <v>116</v>
       </c>
@@ -4540,9 +4612,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
       <c r="G13" s="19" t="s">
         <v>85</v>
       </c>
@@ -4557,9 +4630,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
       <c r="G14" s="19" t="s">
         <v>98</v>
       </c>
@@ -4574,9 +4648,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
       <c r="G15" s="19" t="s">
         <v>106</v>
       </c>
@@ -4591,9 +4666,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
       <c r="G16" s="20" t="s">
         <v>117</v>
       </c>
@@ -4607,7 +4683,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="G17" s="20" t="s">
         <v>119</v>
       </c>
@@ -4621,7 +4701,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
       <c r="G18" s="21" t="s">
         <v>120</v>
       </c>
@@ -4635,85 +4719,97 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
       <c r="K20" s="22"/>
       <c r="L20" s="22"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
       <c r="K21" s="22"/>
       <c r="L21" s="22"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
       <c r="K22" s="22"/>
       <c r="L22" s="22"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -4791,17 +4887,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -4816,11 +4913,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="13" t="s">
         <v>110</v>
       </c>
@@ -4897,7 +4994,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
       <c r="D7" s="18"/>
@@ -4914,10 +5011,19 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>115</v>
       </c>
@@ -4932,9 +5038,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>46</v>
+      </c>
       <c r="G9" s="15" t="s">
         <v>124</v>
       </c>
@@ -4949,9 +5062,12 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="42"/>
       <c r="G10" s="15" t="s">
         <v>85</v>
       </c>
@@ -4966,9 +5082,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
       <c r="G11" s="15" t="s">
         <v>89</v>
       </c>
@@ -4983,9 +5100,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
       <c r="G12" s="15" t="s">
         <v>104</v>
       </c>
@@ -5000,9 +5118,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
       <c r="G13" s="15" t="s">
         <v>105</v>
       </c>
@@ -5017,9 +5136,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
       <c r="G14" s="24" t="s">
         <v>84</v>
       </c>
@@ -5034,9 +5154,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
       <c r="G15" s="24" t="s">
         <v>113</v>
       </c>
@@ -5051,9 +5172,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
       <c r="G16" s="24" t="s">
         <v>106</v>
       </c>
@@ -5067,7 +5189,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="G17" s="24" t="s">
         <v>125</v>
       </c>
@@ -5081,7 +5207,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
       <c r="G18" s="24" t="s">
         <v>98</v>
       </c>
@@ -5095,7 +5225,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
       <c r="G19" s="24" t="s">
         <v>91</v>
       </c>
@@ -5109,7 +5243,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
       <c r="G20" s="19" t="s">
         <v>116</v>
       </c>
@@ -5123,7 +5261,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
       <c r="G21" s="19" t="s">
         <v>118</v>
       </c>
@@ -5137,7 +5279,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G22" s="25" t="s">
         <v>126</v>
       </c>
@@ -5151,7 +5293,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="K23" s="14" t="s">
@@ -5161,7 +5303,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="K24" s="14" t="s">
@@ -5171,49 +5313,49 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -5290,17 +5432,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5315,11 +5458,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="13" t="s">
         <v>128</v>
       </c>
@@ -5396,7 +5539,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
       <c r="D7" s="18"/>
@@ -5413,10 +5556,19 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>132</v>
       </c>
@@ -5431,9 +5583,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="42"/>
       <c r="G9" s="15" t="s">
         <v>133</v>
       </c>
@@ -5448,9 +5607,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
       <c r="G10" s="15" t="s">
         <v>134</v>
       </c>
@@ -5465,9 +5629,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
       <c r="G11" s="15" t="s">
         <v>135</v>
       </c>
@@ -5482,9 +5649,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
       <c r="G12" s="15" t="s">
         <v>136</v>
       </c>
@@ -5499,9 +5669,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
       <c r="G13" s="15" t="s">
         <v>137</v>
       </c>
@@ -5516,9 +5689,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
       <c r="G14" s="15" t="s">
         <v>100</v>
       </c>
@@ -5533,9 +5709,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
       <c r="G15" s="15" t="s">
         <v>129</v>
       </c>
@@ -5550,9 +5727,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
       <c r="G16" s="14" t="s">
         <v>138</v>
       </c>
@@ -5566,7 +5744,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="G17" s="14" t="s">
         <v>139</v>
       </c>
@@ -5580,7 +5762,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
       <c r="G18" s="14" t="s">
         <v>91</v>
       </c>
@@ -5594,7 +5780,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
       <c r="G19" s="14" t="s">
         <v>140</v>
       </c>
@@ -5608,7 +5798,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
       <c r="G20" s="14" t="s">
         <v>141</v>
       </c>
@@ -5622,7 +5816,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
       <c r="G21" s="14" t="s">
         <v>106</v>
       </c>
@@ -5636,7 +5834,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G22" s="14" t="s">
         <v>107</v>
       </c>
@@ -5650,7 +5848,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="14" t="s">
         <v>108</v>
       </c>
@@ -5660,7 +5858,7 @@
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="14" t="s">
         <v>142</v>
       </c>
@@ -5670,7 +5868,7 @@
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="26" t="s">
         <v>143</v>
       </c>
@@ -5680,7 +5878,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="14" t="s">
         <v>145</v>
       </c>
@@ -5690,37 +5888,37 @@
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -5797,17 +5995,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5822,11 +6021,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="13" t="s">
         <v>110</v>
       </c>
@@ -5903,7 +6102,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
       <c r="D7" s="18"/>
@@ -5920,10 +6119,19 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>115</v>
       </c>
@@ -5938,9 +6146,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>46</v>
+      </c>
       <c r="G9" s="15" t="s">
         <v>125</v>
       </c>
@@ -5955,9 +6170,12 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="42"/>
       <c r="G10" s="15" t="s">
         <v>148</v>
       </c>
@@ -5972,9 +6190,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="42"/>
       <c r="G11" s="15" t="s">
         <v>98</v>
       </c>
@@ -5989,9 +6210,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="42"/>
       <c r="G12" s="15" t="s">
         <v>89</v>
       </c>
@@ -6006,9 +6230,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="42"/>
       <c r="G13" s="15" t="s">
         <v>82</v>
       </c>
@@ -6023,9 +6250,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" s="42"/>
       <c r="G14" s="15" t="s">
         <v>124</v>
       </c>
@@ -6040,9 +6270,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="42"/>
       <c r="G15" s="14" t="s">
         <v>140</v>
       </c>
@@ -6057,9 +6290,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="42"/>
       <c r="G16" s="14" t="s">
         <v>149</v>
       </c>
@@ -6073,7 +6309,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="42"/>
       <c r="G17" s="14" t="s">
         <v>100</v>
       </c>
@@ -6087,7 +6329,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="42"/>
       <c r="G18" s="14" t="s">
         <v>150</v>
       </c>
@@ -6101,7 +6349,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" s="42"/>
       <c r="G19" s="14" t="s">
         <v>123</v>
       </c>
@@ -6115,7 +6369,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="42"/>
       <c r="G20" s="14" t="s">
         <v>151</v>
       </c>
@@ -6129,7 +6387,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
       <c r="G21" s="14" t="s">
         <v>152</v>
       </c>
@@ -6143,7 +6405,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="14" t="s">
         <v>91</v>
       </c>
@@ -6153,7 +6415,7 @@
       <c r="K22" s="17"/>
       <c r="L22" s="17"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="14" t="s">
         <v>153</v>
       </c>
@@ -6163,7 +6425,7 @@
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="14" t="s">
         <v>154</v>
       </c>
@@ -6173,7 +6435,7 @@
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="14" t="s">
         <v>155</v>
       </c>
@@ -6183,7 +6445,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="28" t="s">
         <v>105</v>
       </c>
@@ -6193,37 +6455,37 @@
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -6301,17 +6563,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -6326,11 +6589,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="13" t="s">
         <v>110</v>
       </c>
@@ -6407,7 +6670,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
       <c r="D7" s="18"/>
@@ -6424,10 +6687,19 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>82</v>
       </c>
@@ -6442,9 +6714,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="42"/>
       <c r="G9" s="15" t="s">
         <v>161</v>
       </c>
@@ -6459,9 +6738,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="42"/>
       <c r="G10" s="15" t="s">
         <v>85</v>
       </c>
@@ -6475,10 +6761,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="18"/>
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" s="42"/>
       <c r="G11" s="15" t="s">
         <v>129</v>
       </c>
@@ -6493,9 +6786,16 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="42"/>
       <c r="G12" s="15" t="s">
         <v>91</v>
       </c>
@@ -6510,9 +6810,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="43" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
       <c r="G13" s="10" t="s">
         <v>162</v>
       </c>
@@ -6527,9 +6832,14 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
       <c r="G14" s="15" t="s">
         <v>155</v>
       </c>
@@ -6544,9 +6854,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
       <c r="G15" s="14" t="s">
         <v>151</v>
       </c>
@@ -6561,9 +6872,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
       <c r="G16" s="14" t="s">
         <v>139</v>
       </c>
@@ -6577,7 +6889,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="G17" s="14" t="s">
         <v>140</v>
       </c>
@@ -6591,7 +6907,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
       <c r="G18" s="14" t="s">
         <v>108</v>
       </c>
@@ -6605,7 +6925,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
       <c r="G19" s="14" t="s">
         <v>116</v>
       </c>
@@ -6619,7 +6943,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
       <c r="G20" s="14" t="s">
         <v>163</v>
       </c>
@@ -6633,7 +6961,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
       <c r="G21" s="14" t="s">
         <v>91</v>
       </c>
@@ -6647,7 +6979,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="14" t="s">
         <v>100</v>
       </c>
@@ -6661,7 +6993,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="14" t="s">
         <v>150</v>
       </c>
@@ -6671,7 +7003,7 @@
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="14" t="s">
         <v>165</v>
       </c>
@@ -6681,7 +7013,7 @@
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="14" t="s">
         <v>164</v>
       </c>
@@ -6691,7 +7023,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="14" t="s">
         <v>123</v>
       </c>
@@ -6701,37 +7033,37 @@
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -6807,18 +7139,18 @@
   <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -6833,11 +7165,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="31" t="s">
         <v>82</v>
       </c>
@@ -6914,7 +7246,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
       <c r="D7" s="18"/>
@@ -6931,10 +7263,19 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="G8" s="19" t="s">
         <v>169</v>
       </c>
@@ -6948,10 +7289,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="18"/>
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="42"/>
       <c r="G9" s="19" t="s">
         <v>100</v>
       </c>
@@ -6966,9 +7314,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
       <c r="G10" s="19" t="s">
         <v>142</v>
       </c>
@@ -6983,9 +7336,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
       <c r="G11" s="19" t="s">
         <v>172</v>
       </c>
@@ -7000,9 +7358,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
       <c r="G12" s="14" t="s">
         <v>163</v>
       </c>
@@ -7017,9 +7380,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
       <c r="G13" s="14" t="s">
         <v>173</v>
       </c>
@@ -7034,9 +7400,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
       <c r="G14" s="14" t="s">
         <v>174</v>
       </c>
@@ -7051,9 +7420,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
       <c r="G15" s="14" t="s">
         <v>175</v>
       </c>
@@ -7068,9 +7440,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
       <c r="G16" s="15" t="s">
         <v>115</v>
       </c>
@@ -7084,7 +7459,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="42"/>
+      <c r="C17" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="G17" s="15" t="s">
         <v>124</v>
       </c>
@@ -7098,7 +7479,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="42"/>
+      <c r="C18" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
       <c r="G18" s="15" t="s">
         <v>161</v>
       </c>
@@ -7112,7 +7499,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="42"/>
+      <c r="C19" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
       <c r="G19" s="15" t="s">
         <v>171</v>
       </c>
@@ -7126,7 +7519,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
       <c r="G20" s="15" t="s">
         <v>177</v>
       </c>
@@ -7140,7 +7537,11 @@
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
       <c r="G21" s="32" t="s">
         <v>178</v>
       </c>
@@ -7154,67 +7555,67 @@
         <v>179</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="K22" s="17"/>
       <c r="L22" s="17"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
